--- a/DISCIONARIO_DADOS.xlsx
+++ b/DISCIONARIO_DADOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ian_borba\Documents\GitHub\SA_PADARIAALEMAO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8309EB6-A3D1-4FA7-B328-4305C35EAC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10E30599-37FE-4175-ADD3-46E5D0A6BF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E0E67480-1290-41CE-BEDF-B6CDD9423F14}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="124">
   <si>
     <t>TABELA PRODUTOS</t>
   </si>
@@ -225,6 +225,192 @@
   </si>
   <si>
     <t xml:space="preserve">ESSE CAMPO IRÁ ARMAZENAR O CPF DO FUNCIONARIO </t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O ESTADO CIVIL DO FUNCIONARIO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ GUARDAR A UNIDADE FEDERAL DO FUNCIONARIO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ GUARDAR A CIDADE QUE O FUNCIONARIO MORA</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O BAIRRO QUE O FUNCIONARIO MORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESSE CAMPO IRÁ ARMAZENAR O CEP DO FUNCIONARIO </t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O NUMERO DA CASA DO FUNCIONARIO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O LOGRADOURO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR A SENHA DO LOGIN DO FUNCIONARIO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O EMAIL DO LOGIN DO FUNCIONARIO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O NIVEL DE ACESSO DO FUNCIONARIO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR A DATA DE NASCIMENTO DO FUNCIONARIO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO  IRÁ ARMAZENAR A DATA DE ADMISSÃO DO FUNCIONARIO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O CARGO DO FUNCIOANARIO</t>
+  </si>
+  <si>
+    <t>Nome_forn</t>
+  </si>
+  <si>
+    <t>CNPJ</t>
+  </si>
+  <si>
+    <t>Num_empresa</t>
+  </si>
+  <si>
+    <t>Data_fundação</t>
+  </si>
+  <si>
+    <t>VARCHAR(18)</t>
+  </si>
+  <si>
+    <t>INT(11)</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO GUARDARÁ A CHAVE PRIMARIA REFERENTE AO FORNECEDOR</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO GUARDARÁ O NOME DO FORNECEDOR</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ GUARDAR O TELEFONE DO FORNECEDOR</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ GUARDAR O CNPJ DO FORNECEDOR</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ GUARDAR A UNIDADE FEDERAL DO FORNECEDOR</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ GUARDAR A CIDADE QUE O FORNECEDOR MORA</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O BAIRRO QUE O FORNECEDOR MORA</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O CEP DO FORNECEDOR</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O NUMERO DA EMPRESA DO FORNECEDOR</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR A DATA DE FUNDAÇÃO DO FORNECEDOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESSE CAMPO IRÁ ARMAZENAR O LOGRADOURO DO FORNECEDOR </t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O EMAIL DO FORNECEDOR</t>
+  </si>
+  <si>
+    <t>TABELA FORNECEDOR</t>
+  </si>
+  <si>
+    <t>TABELA CATEGORÍAS</t>
+  </si>
+  <si>
+    <t>nome_categorias</t>
+  </si>
+  <si>
+    <t>VARCHAR(100)</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO GUARDARÁ A CHAVE PRIMARIA REFERENTE AO CATEGORÍAS</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O NOME DA CATEGORIA</t>
+  </si>
+  <si>
+    <t>TABELA ITENS_VENDAS</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO GUARDARÁ A CHAVE PRIMARIA REFERENTE A ITENS_VENDAS</t>
+  </si>
+  <si>
+    <t>ID_itensvendas</t>
+  </si>
+  <si>
+    <t>ID_vendas</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR A CHAVE ESTRANGEIRA REFERENTE A VENDAS</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO GUARDARÁ A CHAVE ESTRANGEIRA REFERENTE AO PRODUTO</t>
+  </si>
+  <si>
+    <t>Quanrtidade</t>
+  </si>
+  <si>
+    <t>valor_total</t>
+  </si>
+  <si>
+    <t>decimal(10,2)</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O VALOR TOTAL DA VENDA</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR A QUANTIDADE DE ITENS NA VENDA</t>
+  </si>
+  <si>
+    <t>TABELA NÍVEL</t>
+  </si>
+  <si>
+    <t>nivel_de_acesso</t>
+  </si>
+  <si>
+    <t>INT(1)</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O ID DE ACESSO</t>
+  </si>
+  <si>
+    <t>nome_acesso</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O NOME DO ACESSO DO USUARIO</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO GUARDARÁ A CHAVE PRIMARIA REFERENTE A VENDAS</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR A CHAVE ESTRANGEIRA REFERENTE AO FUNCIOANRIO</t>
+  </si>
+  <si>
+    <t>Venda_data</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO GUARDARÁ A DATA QUE A VENDA FOI REALIZADA</t>
+  </si>
+  <si>
+    <t>Forma_pagamento</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR  A  FORMA DE PAGAMENTO ESCOLHIDA PELO CLINTE</t>
   </si>
 </sst>
 </file>
@@ -367,21 +553,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -393,13 +573,25 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -741,709 +933,1671 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC0BD58-DA6D-4D2F-8BDB-C471F8B94AD8}">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="8"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="11" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="11" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="1"/>
+      <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="11" t="s">
+      <c r="D7" s="2"/>
+      <c r="E7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="1"/>
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="11" t="s">
+      <c r="D8" s="2"/>
+      <c r="E8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="11" t="s">
+      <c r="D9" s="2"/>
+      <c r="E9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="1"/>
+      <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="11" t="s">
+      <c r="D10" s="2"/>
+      <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="9" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="9"/>
+      <c r="C14" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="10" t="s">
+      <c r="D14" s="10"/>
+      <c r="E14" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="1"/>
+      <c r="C15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="11" t="s">
+      <c r="D15" s="2"/>
+      <c r="E15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="1"/>
+      <c r="C16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6" t="s">
+      <c r="D16" s="2"/>
+      <c r="E16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="8"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="11" t="s">
+      <c r="D17" s="2"/>
+      <c r="E17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="11" t="s">
+      <c r="D18" s="2"/>
+      <c r="E18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="1"/>
+      <c r="C19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="11" t="s">
+      <c r="D19" s="2"/>
+      <c r="E19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="1"/>
+      <c r="C20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="11" t="s">
+      <c r="D20" s="2"/>
+      <c r="E20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5" t="s">
+      <c r="B22" s="1"/>
+      <c r="C22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="5" t="s">
+      <c r="B23" s="1"/>
+      <c r="C23" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5" t="s">
+      <c r="B24" s="1"/>
+      <c r="C24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="8"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="1"/>
+      <c r="C25" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="5" t="s">
+      <c r="B26" s="1"/>
+      <c r="C26" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="5" t="s">
+      <c r="B27" s="1"/>
+      <c r="C27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="5" t="s">
+      <c r="B28" s="1"/>
+      <c r="C28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="5" t="s">
+      <c r="B29" s="1"/>
+      <c r="C29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="5" t="s">
+      <c r="B30" s="1"/>
+      <c r="C30" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="5" t="s">
+      <c r="B31" s="1"/>
+      <c r="C31" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="5" t="s">
+      <c r="B32" s="1"/>
+      <c r="C32" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="5" t="s">
+      <c r="B33" s="1"/>
+      <c r="C33" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="10"/>
+      <c r="E38" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="6"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="6"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="6"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="10"/>
+      <c r="E55" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="1"/>
+      <c r="C56" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" s="2"/>
+      <c r="E56" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="6"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+      <c r="M61" s="8"/>
+      <c r="N61" s="8"/>
+      <c r="O61" s="8"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="9"/>
+      <c r="C62" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="10"/>
+      <c r="E62" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="11"/>
+      <c r="O62" s="11"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B63" s="1"/>
+      <c r="C63" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D63" s="2"/>
+      <c r="E63" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B64" s="1"/>
+      <c r="C64" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D64" s="2"/>
+      <c r="E64" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="6"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65" s="1"/>
+      <c r="C65" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" s="2"/>
+      <c r="E65" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B66" s="1"/>
+      <c r="C66" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D66" s="2"/>
+      <c r="E66" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B67" s="1"/>
+      <c r="C67" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D67" s="2"/>
+      <c r="E67" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+      <c r="N70" s="8"/>
+      <c r="O70" s="8"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71" s="9"/>
+      <c r="C71" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="10"/>
+      <c r="E71" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+      <c r="N71" s="11"/>
+      <c r="O71" s="11"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B72" s="1"/>
+      <c r="C72" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D72" s="2"/>
+      <c r="E72" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B73" s="1"/>
+      <c r="C73" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D73" s="2"/>
+      <c r="E73" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="6"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
+      <c r="N77" s="8"/>
+      <c r="O77" s="8"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" s="9"/>
+      <c r="C78" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="10"/>
+      <c r="E78" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
+      <c r="N78" s="11"/>
+      <c r="O78" s="11"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B79" s="1"/>
+      <c r="C79" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D79" s="2"/>
+      <c r="E79" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B80" s="1"/>
+      <c r="C80" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D80" s="2"/>
+      <c r="E80" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="6"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B82" s="1"/>
+      <c r="C82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="91">
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:O33"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:O30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:O31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:O32"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:O27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:O28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:O29"/>
+  <mergeCells count="191">
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="E82:O82"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="E80:O80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="E81:O81"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="E78:O78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="E79:O79"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="E73:O73"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="E77:O77"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="E71:O71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="E72:O72"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:O67"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="E70:O70"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:O65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:O66"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:O63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:O64"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="E61:O61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:O62"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:O57"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:O55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E56:O56"/>
+    <mergeCell ref="E54:O54"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:O49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="E50:O50"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:O47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E48:O48"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:O45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:O46"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:O43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:O44"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:O41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:O42"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:O39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:O40"/>
+    <mergeCell ref="E1:O1"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:O37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E38:O38"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:O14"/>
+    <mergeCell ref="E2:O2"/>
+    <mergeCell ref="E3:O3"/>
+    <mergeCell ref="E5:O5"/>
+    <mergeCell ref="E6:O6"/>
+    <mergeCell ref="E7:O7"/>
+    <mergeCell ref="E4:O4"/>
+    <mergeCell ref="E8:O8"/>
+    <mergeCell ref="E9:O9"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:O10"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:O13"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:O15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:O16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:O17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:O18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:O19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:O20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:O21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:O22"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C23:D23"/>
@@ -1460,64 +2614,23 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:O21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:O22"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:O19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:O20"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:O17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:O18"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:O15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:O16"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:O10"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E13:O13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:O14"/>
-    <mergeCell ref="E2:O2"/>
-    <mergeCell ref="E3:O3"/>
-    <mergeCell ref="E5:O5"/>
-    <mergeCell ref="E6:O6"/>
-    <mergeCell ref="E7:O7"/>
-    <mergeCell ref="E4:O4"/>
-    <mergeCell ref="E8:O8"/>
-    <mergeCell ref="E9:O9"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E1:O1"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:O27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:O28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:O29"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:O33"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:O30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:O31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:O32"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/DISCIONARIO_DADOS.xlsx
+++ b/DISCIONARIO_DADOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ian_borba\Documents\GitHub\SA_PADARIAALEMAO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10E30599-37FE-4175-ADD3-46E5D0A6BF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0966B7F1-6E78-49AC-809C-9E4AB4CF4948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E0E67480-1290-41CE-BEDF-B6CDD9423F14}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="127">
   <si>
     <t>TABELA PRODUTOS</t>
   </si>
@@ -411,13 +411,22 @@
   </si>
   <si>
     <t>ESSE CAMPO IRÁ ARMAZENAR  A  FORMA DE PAGAMENTO ESCOLHIDA PELO CLINTE</t>
+  </si>
+  <si>
+    <t>senha_temporaria</t>
+  </si>
+  <si>
+    <t>tinyint(1)</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR A SENHA TEMPORÁRIA QUE SERA GERADA AUTOMATICAMENTE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -427,6 +436,20 @@
     </font>
     <font>
       <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -553,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -594,6 +617,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -933,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC0BD58-DA6D-4D2F-8BDB-C471F8B94AD8}">
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -943,19 +970,19 @@
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -1171,19 +1198,19 @@
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
@@ -1643,6 +1670,29 @@
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
     </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+    </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>93</v>
@@ -2060,9 +2110,7 @@
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
-      <c r="E61" s="8" t="s">
-        <v>1</v>
-      </c>
+      <c r="E61" s="8"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
@@ -2438,11 +2486,20 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
     </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C92" s="15"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C93" s="15"/>
+    </row>
   </sheetData>
-  <mergeCells count="191">
+  <mergeCells count="194">
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="C82:D82"/>
     <mergeCell ref="E82:O82"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:O34"/>
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="C80:D80"/>
     <mergeCell ref="E80:O80"/>
